--- a/SME.ConectaFormacao.Infra.Dados/Templates/Template_Relatorio_Inscritos_Por_Formacao.xlsx
+++ b/SME.ConectaFormacao.Infra.Dados/Templates/Template_Relatorio_Inscritos_Por_Formacao.xlsx
@@ -1,40 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="30720" windowHeight="8400" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
-  <si>
-    <t xml:space="preserve">CONECTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relatório de inscritos por formação</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+  <si>
+    <t>CONECTA</t>
+  </si>
+  <si>
+    <t>Relatório de inscritos por formação</t>
   </si>
   <si>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Usuário: </t>
@@ -44,7 +50,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">{{Usuario}} </t>
@@ -53,11 +58,10 @@
   <si>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">RF: </t>
@@ -67,20 +71,18 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">{{RF}}</t>
+      <t>{{RF}}</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Data: </t>
@@ -90,83 +92,85 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">{{Data}} </t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Código da formação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Código da homologação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome da formação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Área promotora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretoria Regional (DRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidade Educacional (UE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Período de realização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Situação da formação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modalidade formativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Público-alvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Função específica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etapa/modalidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ano/etapa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Componente curricular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF/CPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome do cursista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Situação da inscrição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Situação da conclusão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-mail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pessoa com deficiência?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual deficiência?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precisa de adaptação?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual tipo de adaptação?</t>
+    <t>Código da formação</t>
+  </si>
+  <si>
+    <t>Código da homologação</t>
+  </si>
+  <si>
+    <t>Nome da formação</t>
+  </si>
+  <si>
+    <t>Área promotora</t>
+  </si>
+  <si>
+    <t>Diretoria Regional (DRE)</t>
+  </si>
+  <si>
+    <t>Unidade Educacional (UE)</t>
+  </si>
+  <si>
+    <t>Período de realização</t>
+  </si>
+  <si>
+    <t>Situação da formação</t>
+  </si>
+  <si>
+    <t>Modalidade formativa</t>
+  </si>
+  <si>
+    <t>Público-alvo</t>
+  </si>
+  <si>
+    <t>Função específica</t>
+  </si>
+  <si>
+    <t>Etapa/modalidade</t>
+  </si>
+  <si>
+    <t>Ano/etapa</t>
+  </si>
+  <si>
+    <t>Componente curricular</t>
+  </si>
+  <si>
+    <t>Turma</t>
+  </si>
+  <si>
+    <t>RF/CPF</t>
+  </si>
+  <si>
+    <t>Nome do cursista</t>
+  </si>
+  <si>
+    <t>Situação da inscrição</t>
+  </si>
+  <si>
+    <t>Situação da conclusão</t>
+  </si>
+  <si>
+    <t>E-mail educacional</t>
+  </si>
+  <si>
+    <t>E-mail</t>
+  </si>
+  <si>
+    <t>Pessoa com deficiência?</t>
+  </si>
+  <si>
+    <t>Qual deficiência?</t>
+  </si>
+  <si>
+    <t>Precisa de adaptação?</t>
+  </si>
+  <si>
+    <t>Qual tipo de adaptação?</t>
   </si>
   <si>
     <t xml:space="preserve">{{inscritos.CodigoFormacao}} </t>
@@ -211,123 +215,255 @@
     <t xml:space="preserve">{{inscritos.Componente}} </t>
   </si>
   <si>
-    <t xml:space="preserve">{{inscritos.Turma}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{inscritos.RfCpf}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{inscritos.Nome}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{inscritos.SituacaoInscricao}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{inscritos.SituacaoConclusao}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{inscritos.Email}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{inscritos.Pcd}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{inscritos.QualDeficiencia}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{inscritos.PrecisaAdaptacao}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{inscritos.QualAdaptacao}}</t>
+    <t>{{inscritos.Turma}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.RfCpf}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.Nome}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.SituacaoInscricao}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.SituacaoConclusao}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.Email}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.EmailNaoEducacional}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.Pcd}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.QualDeficiencia}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.PrecisaAdaptacao}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.QualAdaptacao}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;* #,##0_-;\-&quot;R$&quot;* #,##0_-;_-&quot;R$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,16 +476,202 @@
         <bgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="12">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color theme="0" tint="-0.25"/>
       </left>
@@ -362,7 +684,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color theme="0" tint="-0.25"/>
       </left>
@@ -373,7 +695,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color theme="0" tint="-0.25"/>
       </left>
@@ -384,191 +706,649 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
+    <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Moeda [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Hyperlink seguido" xfId="7" builtinId="9"/>
+    <cellStyle name="Observação" xfId="8" builtinId="10"/>
+    <cellStyle name="Texto de Aviso" xfId="9" builtinId="11"/>
+    <cellStyle name="Título" xfId="10" builtinId="15"/>
+    <cellStyle name="Texto Explicativo" xfId="11" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
+    <cellStyle name="Saída" xfId="17" builtinId="21"/>
+    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
+    <cellStyle name="Célula de Verificação" xfId="19" builtinId="23"/>
+    <cellStyle name="Célula Vinculada" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Bom" xfId="22" builtinId="26"/>
+    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
+    <cellStyle name="Ênfase 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Ênfase 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Ênfase 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Ênfase 1" xfId="28" builtinId="32"/>
+    <cellStyle name="Ênfase 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Ênfase 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Ênfase 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Ênfase 2" xfId="32" builtinId="36"/>
+    <cellStyle name="Ênfase 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Ênfase 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Ênfase 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Ênfase 3" xfId="36" builtinId="40"/>
+    <cellStyle name="Ênfase 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Ênfase 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Ênfase 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Ênfase 4" xfId="40" builtinId="44"/>
+    <cellStyle name="Ênfase 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Ênfase 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Ênfase 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Ênfase 5" xfId="44" builtinId="48"/>
+    <cellStyle name="Ênfase 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Ênfase 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Ênfase 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00BFBFBF"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00D9D9D9"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -584,17 +1364,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Imagem 1" descr=""/>
+        <xdr:cNvPr id="2" name="Imagem 1"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
-        <a:stretch/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="552600" y="295200"/>
-          <a:ext cx="1960560" cy="552240"/>
+          <a:off x="552450" y="294640"/>
+          <a:ext cx="1894205" cy="560705"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -611,59 +1393,59 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -690,7 +1472,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -714,7 +1496,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -774,35 +1556,34 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:AX8"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:BA8"/>
+  <sheetFormatPr defaultColWidth="11.537037037037" defaultRowHeight="15" customHeight="1" outlineLevelRow="7"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="1" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="17" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="15.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="25" style="0" width="15.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="33" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="36" style="0" width="8.68"/>
+    <col min="1" max="15" width="17.287037037037" customWidth="1"/>
+    <col min="16" max="16" width="19" customWidth="1"/>
+    <col min="17" max="20" width="17.287037037037" customWidth="1"/>
+    <col min="21" max="21" width="21.4259259259259" customWidth="1"/>
+    <col min="22" max="22" width="15.712962962963" customWidth="1"/>
+    <col min="23" max="23" width="15.1388888888889" customWidth="1"/>
+    <col min="24" max="24" width="15.287037037037" customWidth="1"/>
+    <col min="25" max="32" width="15.8518518518519" customWidth="1"/>
+    <col min="33" max="35" width="19" customWidth="1"/>
+    <col min="36" max="50" width="8.67592592592593" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customHeight="1" spans="1:53">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -856,7 +1637,7 @@
       <c r="AW1" s="2"/>
       <c r="AX1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="23.25" customHeight="1" spans="1:53">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -908,7 +1689,7 @@
       <c r="AW2" s="2"/>
       <c r="AX2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="18" spans="1:53">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -962,7 +1743,7 @@
       <c r="AW3" s="3"/>
       <c r="AX3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="14.4" spans="1:53">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1014,7 +1795,7 @@
       <c r="AW4" s="1"/>
       <c r="AX4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="14.4" spans="1:53">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1032,7 +1813,7 @@
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="14.4" spans="1:53">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1069,7 +1850,7 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="23.85" customHeight="1" spans="1:53">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -1145,134 +1926,142 @@
       </c>
       <c r="AH7" s="11"/>
       <c r="AI7" s="11"/>
-      <c r="AJ7" s="13" t="s">
+      <c r="AJ7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="AK7" s="13"/>
-      <c r="AL7" s="13"/>
+      <c r="AK7" s="11"/>
+      <c r="AL7" s="11"/>
       <c r="AM7" s="13" t="s">
         <v>26</v>
       </c>
       <c r="AN7" s="13"/>
       <c r="AO7" s="13"/>
-      <c r="AP7" s="13"/>
-      <c r="AQ7" s="13" t="s">
+      <c r="AP7" s="13" t="s">
         <v>27</v>
       </c>
+      <c r="AQ7" s="13"/>
       <c r="AR7" s="13"/>
       <c r="AS7" s="13"/>
-      <c r="AT7" s="13"/>
-      <c r="AU7" s="13" t="s">
+      <c r="AT7" s="13" t="s">
         <v>28</v>
       </c>
+      <c r="AU7" s="13"/>
       <c r="AV7" s="13"/>
       <c r="AW7" s="13"/>
-      <c r="AX7" s="13"/>
+      <c r="AX7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="AY7" s="13"/>
+      <c r="AZ7" s="13"/>
+      <c r="BA7" s="13"/>
     </row>
-    <row r="8" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="33" customHeight="1" spans="1:53">
       <c r="A8" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O8" s="17"/>
       <c r="P8" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T8" s="15"/>
       <c r="U8" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V8" s="15"/>
       <c r="W8" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X8" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Y8" s="15"/>
       <c r="Z8" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AA8" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AB8" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AC8" s="16"/>
       <c r="AD8" s="16"/>
       <c r="AE8" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF8" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG8" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AH8" s="16"/>
       <c r="AI8" s="16"/>
-      <c r="AJ8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK8" s="20"/>
-      <c r="AL8" s="20"/>
-      <c r="AM8" s="19" t="s">
+      <c r="AJ8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
-      <c r="AP8" s="19"/>
-      <c r="AQ8" s="20" t="s">
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="16"/>
+      <c r="AM8" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="AR8" s="20"/>
-      <c r="AS8" s="20"/>
-      <c r="AT8" s="20"/>
-      <c r="AU8" s="16" t="s">
+      <c r="AN8" s="20"/>
+      <c r="AO8" s="20"/>
+      <c r="AP8" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AV8" s="16"/>
-      <c r="AW8" s="16"/>
-      <c r="AX8" s="16"/>
+      <c r="AQ8" s="19"/>
+      <c r="AR8" s="19"/>
+      <c r="AS8" s="19"/>
+      <c r="AT8" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU8" s="20"/>
+      <c r="AV8" s="20"/>
+      <c r="AW8" s="20"/>
+      <c r="AX8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="AY8" s="16"/>
+      <c r="AZ8" s="16"/>
+      <c r="BA8" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A1:C5"/>
-    <mergeCell ref="D1:AX2"/>
+  <mergeCells count="38">
     <mergeCell ref="D3:AX3"/>
     <mergeCell ref="D4:AX4"/>
     <mergeCell ref="D5:F5"/>
@@ -1290,9 +2079,10 @@
     <mergeCell ref="AB7:AD7"/>
     <mergeCell ref="AG7:AI7"/>
     <mergeCell ref="AJ7:AL7"/>
-    <mergeCell ref="AM7:AP7"/>
-    <mergeCell ref="AQ7:AT7"/>
-    <mergeCell ref="AU7:AX7"/>
+    <mergeCell ref="AM7:AO7"/>
+    <mergeCell ref="AP7:AS7"/>
+    <mergeCell ref="AT7:AW7"/>
+    <mergeCell ref="AX7:BA7"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="H8:J8"/>
@@ -1304,17 +2094,16 @@
     <mergeCell ref="AB8:AD8"/>
     <mergeCell ref="AG8:AI8"/>
     <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AM8:AP8"/>
-    <mergeCell ref="AQ8:AT8"/>
-    <mergeCell ref="AU8:AX8"/>
+    <mergeCell ref="AM8:AO8"/>
+    <mergeCell ref="AP8:AS8"/>
+    <mergeCell ref="AT8:AW8"/>
+    <mergeCell ref="AX8:BA8"/>
+    <mergeCell ref="A1:C5"/>
+    <mergeCell ref="D1:AX2"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/SME.ConectaFormacao.Infra.Dados/Templates/Template_Relatorio_Inscritos_Por_Formacao.xlsx
+++ b/SME.ConectaFormacao.Infra.Dados/Templates/Template_Relatorio_Inscritos_Por_Formacao.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="8400" tabRatio="500"/>
+    <workbookView windowWidth="30720" windowHeight="7800" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>CONECTA</t>
   </si>
@@ -152,6 +152,9 @@
     <t>Situação da inscrição</t>
   </si>
   <si>
+    <t>Telefone</t>
+  </si>
+  <si>
     <t>Situação da conclusão</t>
   </si>
   <si>
@@ -225,6 +228,9 @@
   </si>
   <si>
     <t>{{inscritos.SituacaoInscricao}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.Telefone}}</t>
   </si>
   <si>
     <t>{{inscritos.SituacaoConclusao}}</t>
@@ -1568,7 +1574,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BA8"/>
+  <dimension ref="A1:BB8"/>
   <sheetFormatPr defaultColWidth="11.537037037037" defaultRowHeight="15" customHeight="1" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="15" width="17.287037037037" customWidth="1"/>
@@ -1583,7 +1589,7 @@
     <col min="36" max="50" width="8.67592592592593" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:53">
+    <row r="1" customHeight="1" spans="1:54">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1637,7 +1643,7 @@
       <c r="AW1" s="2"/>
       <c r="AX1" s="2"/>
     </row>
-    <row r="2" ht="23.25" customHeight="1" spans="1:53">
+    <row r="2" ht="23.25" customHeight="1" spans="1:54">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1689,7 +1695,7 @@
       <c r="AW2" s="2"/>
       <c r="AX2" s="2"/>
     </row>
-    <row r="3" ht="18" spans="1:53">
+    <row r="3" ht="18" spans="1:54">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1743,7 +1749,7 @@
       <c r="AW3" s="3"/>
       <c r="AX3" s="3"/>
     </row>
-    <row r="4" ht="14.4" spans="1:53">
+    <row r="4" ht="14.4" spans="1:54">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1795,7 +1801,7 @@
       <c r="AW4" s="1"/>
       <c r="AX4" s="1"/>
     </row>
-    <row r="5" ht="14.4" spans="1:53">
+    <row r="5" ht="14.4" spans="1:54">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1813,7 +1819,7 @@
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" ht="14.4" spans="1:53">
+    <row r="6" ht="14.4" spans="1:54">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1850,7 +1856,7 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" ht="23.85" customHeight="1" spans="1:53">
+    <row r="7" ht="23.85" customHeight="1" spans="1:54">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -1921,144 +1927,150 @@
       <c r="AF7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AG7" s="11" t="s">
+      <c r="AG7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AH7" s="11"/>
+      <c r="AH7" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="AI7" s="11"/>
-      <c r="AJ7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK7" s="11"/>
+      <c r="AJ7" s="11"/>
+      <c r="AK7" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="AL7" s="11"/>
-      <c r="AM7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN7" s="13"/>
+      <c r="AM7" s="11"/>
+      <c r="AN7" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="AO7" s="13"/>
-      <c r="AP7" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="AQ7" s="13"/>
+      <c r="AP7" s="13"/>
+      <c r="AQ7" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="AR7" s="13"/>
       <c r="AS7" s="13"/>
-      <c r="AT7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="AU7" s="13"/>
+      <c r="AT7" s="13"/>
+      <c r="AU7" s="13" t="s">
+        <v>29</v>
+      </c>
       <c r="AV7" s="13"/>
       <c r="AW7" s="13"/>
-      <c r="AX7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="AY7" s="13"/>
+      <c r="AX7" s="13"/>
+      <c r="AY7" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="AZ7" s="13"/>
       <c r="BA7" s="13"/>
+      <c r="BB7" s="13"/>
     </row>
-    <row r="8" ht="33" customHeight="1" spans="1:53">
+    <row r="8" ht="33" customHeight="1" spans="1:54">
       <c r="A8" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O8" s="17"/>
       <c r="P8" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T8" s="15"/>
       <c r="U8" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V8" s="15"/>
       <c r="W8" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X8" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y8" s="15"/>
       <c r="Z8" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA8" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AB8" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AC8" s="16"/>
       <c r="AD8" s="16"/>
       <c r="AE8" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AG8" s="16" t="s">
+      <c r="AF8" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="AH8" s="16"/>
+      <c r="AG8" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH8" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="AI8" s="16"/>
-      <c r="AJ8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK8" s="16"/>
+      <c r="AJ8" s="16"/>
+      <c r="AK8" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="AL8" s="16"/>
-      <c r="AM8" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="AN8" s="20"/>
+      <c r="AM8" s="16"/>
+      <c r="AN8" s="20" t="s">
+        <v>53</v>
+      </c>
       <c r="AO8" s="20"/>
-      <c r="AP8" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="AQ8" s="19"/>
+      <c r="AP8" s="20"/>
+      <c r="AQ8" s="19" t="s">
+        <v>54</v>
+      </c>
       <c r="AR8" s="19"/>
       <c r="AS8" s="19"/>
-      <c r="AT8" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="AU8" s="20"/>
+      <c r="AT8" s="19"/>
+      <c r="AU8" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="AV8" s="20"/>
       <c r="AW8" s="20"/>
-      <c r="AX8" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="AY8" s="16"/>
+      <c r="AX8" s="20"/>
+      <c r="AY8" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="AZ8" s="16"/>
       <c r="BA8" s="16"/>
+      <c r="BB8" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="38">
@@ -2077,12 +2089,12 @@
     <mergeCell ref="U7:V7"/>
     <mergeCell ref="X7:Y7"/>
     <mergeCell ref="AB7:AD7"/>
-    <mergeCell ref="AG7:AI7"/>
-    <mergeCell ref="AJ7:AL7"/>
-    <mergeCell ref="AM7:AO7"/>
-    <mergeCell ref="AP7:AS7"/>
-    <mergeCell ref="AT7:AW7"/>
-    <mergeCell ref="AX7:BA7"/>
+    <mergeCell ref="AH7:AJ7"/>
+    <mergeCell ref="AK7:AM7"/>
+    <mergeCell ref="AN7:AP7"/>
+    <mergeCell ref="AQ7:AT7"/>
+    <mergeCell ref="AU7:AX7"/>
+    <mergeCell ref="AY7:BB7"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="H8:J8"/>
@@ -2092,12 +2104,12 @@
     <mergeCell ref="U8:V8"/>
     <mergeCell ref="X8:Y8"/>
     <mergeCell ref="AB8:AD8"/>
-    <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AJ8:AL8"/>
-    <mergeCell ref="AM8:AO8"/>
-    <mergeCell ref="AP8:AS8"/>
-    <mergeCell ref="AT8:AW8"/>
-    <mergeCell ref="AX8:BA8"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AK8:AM8"/>
+    <mergeCell ref="AN8:AP8"/>
+    <mergeCell ref="AQ8:AT8"/>
+    <mergeCell ref="AU8:AX8"/>
+    <mergeCell ref="AY8:BB8"/>
     <mergeCell ref="A1:C5"/>
     <mergeCell ref="D1:AX2"/>
   </mergeCells>

--- a/SME.ConectaFormacao.Infra.Dados/Templates/Template_Relatorio_Inscritos_Por_Formacao.xlsx
+++ b/SME.ConectaFormacao.Infra.Dados/Templates/Template_Relatorio_Inscritos_Por_Formacao.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="7800" tabRatio="500"/>
+    <workbookView windowWidth="30720" windowHeight="8400" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>CONECTA</t>
   </si>
@@ -152,6 +152,12 @@
     <t>Situação da inscrição</t>
   </si>
   <si>
+    <t>Data da inscrição</t>
+  </si>
+  <si>
+    <t>Hora da inscrição</t>
+  </si>
+  <si>
     <t>Telefone</t>
   </si>
   <si>
@@ -230,10 +236,10 @@
     <t>{{inscritos.SituacaoInscricao}}</t>
   </si>
   <si>
-    <t>{{inscritos.Telefone}}</t>
-  </si>
-  <si>
-    <t>{{inscritos.SituacaoConclusao}}</t>
+    <t>{{inscritos.DataInscricao}}</t>
+  </si>
+  <si>
+    <t>{{inscritos.HoraInscricao}}</t>
   </si>
   <si>
     <t>{{inscritos.Email}}</t>
@@ -1574,7 +1580,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BB8"/>
+  <dimension ref="A1:BD8"/>
   <sheetFormatPr defaultColWidth="11.537037037037" defaultRowHeight="15" customHeight="1" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="15" width="17.287037037037" customWidth="1"/>
@@ -1589,7 +1595,7 @@
     <col min="36" max="50" width="8.67592592592593" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:54">
+    <row r="1" customHeight="1" spans="1:56">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1643,7 +1649,7 @@
       <c r="AW1" s="2"/>
       <c r="AX1" s="2"/>
     </row>
-    <row r="2" ht="23.25" customHeight="1" spans="1:54">
+    <row r="2" ht="23.25" customHeight="1" spans="1:56">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1695,7 +1701,7 @@
       <c r="AW2" s="2"/>
       <c r="AX2" s="2"/>
     </row>
-    <row r="3" ht="18" spans="1:54">
+    <row r="3" ht="18" spans="1:56">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1749,7 +1755,7 @@
       <c r="AW3" s="3"/>
       <c r="AX3" s="3"/>
     </row>
-    <row r="4" ht="14.4" spans="1:54">
+    <row r="4" ht="14.4" spans="1:56">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1801,7 +1807,7 @@
       <c r="AW4" s="1"/>
       <c r="AX4" s="1"/>
     </row>
-    <row r="5" ht="14.4" spans="1:54">
+    <row r="5" ht="14.4" spans="1:56">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1819,7 +1825,7 @@
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" ht="14.4" spans="1:54">
+    <row r="6" ht="14.4" spans="1:56">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1856,7 +1862,7 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" ht="23.85" customHeight="1" spans="1:54">
+    <row r="7" ht="23.85" customHeight="1" spans="1:56">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -1924,149 +1930,155 @@
       <c r="AE7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="AF7" s="12" t="s">
+      <c r="AF7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="AG7" s="12" t="s">
+      <c r="AG7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="AH7" s="11" t="s">
+      <c r="AH7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AI7" s="11"/>
-      <c r="AJ7" s="11"/>
-      <c r="AK7" s="11" t="s">
+      <c r="AI7" s="12" t="s">
         <v>26</v>
       </c>
+      <c r="AJ7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK7" s="11"/>
       <c r="AL7" s="11"/>
-      <c r="AM7" s="11"/>
-      <c r="AN7" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="AO7" s="13"/>
-      <c r="AP7" s="13"/>
-      <c r="AQ7" s="13" t="s">
+      <c r="AM7" s="11" t="s">
         <v>28</v>
       </c>
+      <c r="AN7" s="11"/>
+      <c r="AO7" s="11"/>
+      <c r="AP7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="AQ7" s="13"/>
       <c r="AR7" s="13"/>
-      <c r="AS7" s="13"/>
+      <c r="AS7" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="AT7" s="13"/>
-      <c r="AU7" s="13" t="s">
-        <v>29</v>
-      </c>
+      <c r="AU7" s="13"/>
       <c r="AV7" s="13"/>
-      <c r="AW7" s="13"/>
+      <c r="AW7" s="13" t="s">
+        <v>31</v>
+      </c>
       <c r="AX7" s="13"/>
-      <c r="AY7" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="AY7" s="13"/>
       <c r="AZ7" s="13"/>
-      <c r="BA7" s="13"/>
+      <c r="BA7" s="13" t="s">
+        <v>32</v>
+      </c>
       <c r="BB7" s="13"/>
+      <c r="BC7" s="13"/>
+      <c r="BD7" s="13"/>
     </row>
-    <row r="8" ht="33" customHeight="1" spans="1:54">
+    <row r="8" ht="33" customHeight="1" spans="1:56">
       <c r="A8" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O8" s="17"/>
       <c r="P8" s="18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R8" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T8" s="15"/>
       <c r="U8" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V8" s="15"/>
       <c r="W8" s="15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X8" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y8" s="15"/>
       <c r="Z8" s="19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AA8" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB8" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AC8" s="16"/>
       <c r="AD8" s="16"/>
       <c r="AE8" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF8" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AG8" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AH8" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AI8" s="16"/>
       <c r="AJ8" s="16"/>
       <c r="AK8" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AL8" s="16"/>
       <c r="AM8" s="16"/>
       <c r="AN8" s="20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AO8" s="20"/>
       <c r="AP8" s="20"/>
       <c r="AQ8" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AR8" s="19"/>
       <c r="AS8" s="19"/>
       <c r="AT8" s="19"/>
       <c r="AU8" s="20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AV8" s="20"/>
       <c r="AW8" s="20"/>
       <c r="AX8" s="20"/>
       <c r="AY8" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AZ8" s="16"/>
       <c r="BA8" s="16"/>
@@ -2089,12 +2101,12 @@
     <mergeCell ref="U7:V7"/>
     <mergeCell ref="X7:Y7"/>
     <mergeCell ref="AB7:AD7"/>
-    <mergeCell ref="AH7:AJ7"/>
-    <mergeCell ref="AK7:AM7"/>
-    <mergeCell ref="AN7:AP7"/>
-    <mergeCell ref="AQ7:AT7"/>
-    <mergeCell ref="AU7:AX7"/>
-    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="AJ7:AL7"/>
+    <mergeCell ref="AM7:AO7"/>
+    <mergeCell ref="AP7:AR7"/>
+    <mergeCell ref="AS7:AV7"/>
+    <mergeCell ref="AW7:AZ7"/>
+    <mergeCell ref="BA7:BD7"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="H8:J8"/>
